--- a/2026/SAEN PEÑA/ENERO/SAENZ_EXPENSAS-Enero.xlsx
+++ b/2026/SAEN PEÑA/ENERO/SAENZ_EXPENSAS-Enero.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\SAEN PEÑA\ENERO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\2026\SAEN PEÑA\ENERO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9011F504-B8AD-4DFE-A73D-3CEF02F0028C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34B4E8AD-90D8-4CDA-865D-658D9CAC82C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="extraordinaria" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$F$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$F$35</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
@@ -247,7 +247,7 @@
     <t xml:space="preserve">Período ENERO </t>
   </si>
   <si>
-    <t>SAC - ENERO - Sra. Nancy</t>
+    <t>Subidos en En3r0</t>
   </si>
 </sst>
 </file>
@@ -262,7 +262,7 @@
     <numFmt numFmtId="167" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="168" formatCode="_ &quot;$&quot;\ * #,##0.0_ ;_ &quot;$&quot;\ * \-#,##0.0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -370,13 +370,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -1066,7 +1059,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="151">
+  <cellXfs count="149">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1342,8 +1335,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="15" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1711,23 +1702,23 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H63"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
-    <col min="3" max="3" width="13.5546875" customWidth="1"/>
-    <col min="4" max="4" width="7.5546875" customWidth="1"/>
-    <col min="5" max="5" width="58.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5546875" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" customWidth="1"/>
+    <col min="4" max="4" width="7.5703125" customWidth="1"/>
+    <col min="5" max="5" width="58.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>20</v>
       </c>
@@ -1735,27 +1726,27 @@
         <v>62</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="23"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D6" s="28"/>
       <c r="E6" s="28"/>
       <c r="F6" s="28"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="24" t="s">
         <v>43</v>
       </c>
@@ -1767,7 +1758,7 @@
       </c>
       <c r="F7" s="98"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -1775,12 +1766,12 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="101" t="s">
         <v>12</v>
       </c>
@@ -1792,7 +1783,7 @@
       </c>
       <c r="F11" s="129"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="99"/>
       <c r="B12" s="99"/>
       <c r="C12" s="122"/>
@@ -1801,17 +1792,17 @@
         <v>48</v>
       </c>
       <c r="F12" s="121">
-        <v>1555952.8226141399</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1616917.9192361401</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="97" t="s">
         <v>64</v>
       </c>
       <c r="B13" s="97" t="s">
         <v>65</v>
       </c>
-      <c r="C13" s="149">
+      <c r="C13" s="105">
         <v>37185.11</v>
       </c>
       <c r="D13" s="36"/>
@@ -1820,17 +1811,17 @@
       </c>
       <c r="F13" s="50">
         <f>'prorrateo '!F11</f>
-        <v>276680.51862200012</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+        <v>344271.84</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="99" t="s">
         <v>26</v>
       </c>
       <c r="B14" s="99" t="s">
         <v>61</v>
       </c>
-      <c r="C14" s="149">
+      <c r="C14" s="105">
         <v>39011.1</v>
       </c>
       <c r="D14" s="5"/>
@@ -1838,11 +1829,11 @@
         <v>22</v>
       </c>
       <c r="F14" s="50">
-        <f>-(C36)</f>
-        <v>-224478.36199999994</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+        <f>-(C35)</f>
+        <v>-246950.41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="97" t="s">
         <v>21</v>
       </c>
@@ -1850,40 +1841,43 @@
         <v>66</v>
       </c>
       <c r="C15" s="71">
-        <v>32800</v>
+        <v>35000</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="49"/>
       <c r="F15" s="50"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="99" t="s">
         <v>70</v>
       </c>
       <c r="B16" s="97"/>
-      <c r="C16" s="150">
+      <c r="C16" s="71">
         <v>10568</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="49"/>
       <c r="F16" s="50"/>
-    </row>
-    <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H16" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="102"/>
       <c r="B17" s="103"/>
       <c r="C17" s="126">
         <f>SUM(C12:C16)</f>
-        <v>119564.20999999999</v>
+        <v>121764.20999999999</v>
       </c>
       <c r="E17" s="51" t="s">
         <v>49</v>
       </c>
       <c r="F17" s="118">
         <f>SUM(F12:F15)</f>
-        <v>1608154.9792361401</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1714239.3492361403</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="101" t="s">
         <v>23</v>
       </c>
@@ -1893,7 +1887,7 @@
       <c r="E18" s="19"/>
       <c r="F18" s="20"/>
     </row>
-    <row r="19" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="97" t="s">
         <v>42</v>
       </c>
@@ -1901,228 +1895,217 @@
         <v>72</v>
       </c>
       <c r="C19" s="71">
-        <f xml:space="preserve"> 58285.64+58285.64*20%</f>
-        <v>69942.767999999996</v>
+        <f xml:space="preserve"> 69942+69942*10%</f>
+        <v>76936.2</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="19"/>
       <c r="F19" s="20"/>
     </row>
-    <row r="20" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="97" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B20" s="104"/>
-      <c r="C20" s="71">
-        <f>C19/2</f>
-        <v>34971.383999999998</v>
+      <c r="C20" s="105">
+        <v>48250</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="19"/>
       <c r="F20" s="20"/>
     </row>
-    <row r="21" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="97" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B21" s="104"/>
-      <c r="C21" s="122"/>
+      <c r="C21" s="105">
+        <f>400000-246950.4</f>
+        <v>153049.60000000001</v>
+      </c>
       <c r="D21" s="5"/>
       <c r="E21" s="19"/>
       <c r="F21" s="20"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="97" t="s">
-        <v>67</v>
-      </c>
-      <c r="B22" s="104"/>
-      <c r="C22" s="105">
-        <f>400000-215715.4</f>
-        <v>184284.6</v>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="102"/>
+      <c r="B22" s="103"/>
+      <c r="C22" s="119">
+        <f>SUM(C18:C21)</f>
+        <v>278235.8</v>
       </c>
       <c r="D22" s="5"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="20"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="102"/>
-      <c r="B23" s="103"/>
-      <c r="C23" s="119">
-        <f>SUM(C18:C22)</f>
-        <v>289198.75199999998</v>
+      <c r="E22" s="5"/>
+      <c r="F22" s="47"/>
+      <c r="G22" s="6"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" s="41"/>
+      <c r="C23" s="120">
+        <f>+C22+C17</f>
+        <v>400000.01</v>
       </c>
       <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="47"/>
-      <c r="G23" s="6"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="40" t="s">
-        <v>14</v>
-      </c>
-      <c r="B24" s="41"/>
-      <c r="C24" s="120">
-        <f>+C23+C17</f>
-        <v>408762.96199999994</v>
-      </c>
-      <c r="D24" s="5"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="20"/>
+    </row>
+    <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="60" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" s="73"/>
+      <c r="C24" s="74"/>
       <c r="E24" s="19"/>
       <c r="F24" s="20"/>
     </row>
-    <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="60" t="s">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="73"/>
-      <c r="C25" s="74"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="20"/>
-    </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="22" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="37"/>
-      <c r="B27" s="28"/>
-      <c r="C27" s="46"/>
+    </row>
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="37"/>
+      <c r="B26" s="28"/>
+      <c r="C26" s="46"/>
+      <c r="F26" s="6"/>
+    </row>
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="44"/>
+      <c r="B27" s="43"/>
+      <c r="C27" s="45">
+        <v>0</v>
+      </c>
       <c r="F27" s="6"/>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="44"/>
-      <c r="B28" s="43"/>
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="52"/>
+      <c r="B28" s="53"/>
       <c r="C28" s="45">
         <v>0</v>
       </c>
       <c r="F28" s="6"/>
     </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="52"/>
-      <c r="B29" s="53"/>
-      <c r="C29" s="45">
-        <v>0</v>
-      </c>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="69"/>
+      <c r="B29" s="70"/>
+      <c r="C29" s="72"/>
       <c r="F29" s="6"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="69"/>
-      <c r="B30" s="70"/>
-      <c r="C30" s="72"/>
+      <c r="B30" s="76"/>
+      <c r="C30" s="77"/>
       <c r="F30" s="6"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="69"/>
-      <c r="B31" s="76"/>
-      <c r="C31" s="77"/>
+      <c r="B31" s="75"/>
+      <c r="C31" s="72">
+        <v>0</v>
+      </c>
       <c r="F31" s="6"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="69"/>
-      <c r="B32" s="75"/>
-      <c r="C32" s="72">
-        <v>0</v>
-      </c>
-      <c r="F32" s="6"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="54" t="s">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="54" t="s">
         <v>25</v>
       </c>
-      <c r="B33" s="55"/>
-      <c r="C33" s="56">
-        <f>SUM(C28:C32)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+      <c r="B32" s="55"/>
+      <c r="C32" s="56">
+        <f>SUM(C27:C31)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>59</v>
       </c>
-      <c r="C34" s="123">
-        <f>C24-C22</f>
-        <v>224478.36199999994</v>
-      </c>
+      <c r="C33" s="123">
+        <f>C23-C21</f>
+        <v>246950.41</v>
+      </c>
+      <c r="F33" s="6"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C34" s="124">
+        <f>+C23</f>
+        <v>400000.01</v>
+      </c>
+      <c r="E34" s="100"/>
       <c r="F34" s="6"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C35" s="124">
-        <f>+C24</f>
-        <v>408762.96199999994</v>
-      </c>
-      <c r="E35" s="100"/>
-      <c r="F35" s="6"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="54" t="s">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="B36" s="55"/>
-      <c r="C36" s="125">
-        <f>C34</f>
-        <v>224478.36199999994</v>
-      </c>
-      <c r="E36" s="16"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D41" s="6"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B35" s="55"/>
+      <c r="C35" s="125">
+        <f>C33</f>
+        <v>246950.41</v>
+      </c>
+      <c r="E35" s="16"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D40" s="6"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D41" s="16"/>
+      <c r="E41" s="16"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D42" s="16"/>
       <c r="E42" s="16"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D43" s="16"/>
-      <c r="E43" s="16"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D44" s="16"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D45" s="16"/>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" s="19"/>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="19"/>
+      <c r="B56" s="18"/>
+      <c r="C56" s="20"/>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="18"/>
       <c r="B57" s="18"/>
-      <c r="C57" s="20"/>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C57" s="18"/>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="18"/>
       <c r="B58" s="18"/>
       <c r="C58" s="18"/>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="18"/>
       <c r="B59" s="18"/>
       <c r="C59" s="18"/>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="18"/>
       <c r="B60" s="18"/>
       <c r="C60" s="18"/>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="18"/>
       <c r="B61" s="18"/>
       <c r="C61" s="18"/>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="18"/>
       <c r="B62" s="18"/>
       <c r="C62" s="18"/>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="18"/>
       <c r="B63" s="18"/>
       <c r="C63" s="18"/>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" s="18"/>
-      <c r="B64" s="18"/>
-      <c r="C64" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2144,24 +2127,24 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" customWidth="1"/>
-    <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
-    <col min="8" max="8" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.44140625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="12.6640625" customWidth="1"/>
-    <col min="11" max="11" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.44140625" style="21"/>
+    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.42578125" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.42578125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="95" t="s">
         <v>60</v>
       </c>
@@ -2183,7 +2166,7 @@
       </c>
       <c r="L1" s="27"/>
     </row>
-    <row r="2" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="63" t="str">
         <f>'detalle y gastos'!E7</f>
         <v>Liquidacion mes de ENERO</v>
@@ -2202,7 +2185,7 @@
       <c r="K2" s="67"/>
       <c r="L2" s="68"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -2240,7 +2223,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -2270,7 +2253,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="12">
         <v>1</v>
       </c>
@@ -2284,16 +2267,16 @@
         <v>0.1512</v>
       </c>
       <c r="E5" s="34">
-        <v>373213.68854442623</v>
+        <v>465043.63838215801</v>
       </c>
       <c r="F5" s="71"/>
       <c r="G5" s="58">
         <f>E5-F5</f>
-        <v>373213.68854442623</v>
+        <v>465043.63838215801</v>
       </c>
       <c r="H5" s="61">
         <f>IF(G5&gt;0,G5*8.4%,0)</f>
-        <v>31349.949837731805</v>
+        <v>39063.665624101275</v>
       </c>
       <c r="I5" s="15">
         <v>0</v>
@@ -2308,10 +2291,10 @@
       </c>
       <c r="L5" s="32">
         <f>J5+K5+H5+G5</f>
-        <v>465043.63838215801</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+        <v>564587.30400625931</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="12">
         <v>2</v>
       </c>
@@ -2325,16 +2308,19 @@
         <v>0.15690000000000001</v>
       </c>
       <c r="E6" s="34">
-        <v>62760.000000000007</v>
-      </c>
-      <c r="F6" s="128"/>
+        <v>130791.84000000003</v>
+      </c>
+      <c r="F6" s="128">
+        <f>E6</f>
+        <v>130791.84000000003</v>
+      </c>
       <c r="G6" s="58">
         <f t="shared" ref="G6:G8" si="0">E6-F6</f>
-        <v>62760.000000000007</v>
+        <v>0</v>
       </c>
       <c r="H6" s="61">
         <f t="shared" ref="H6:H10" si="1">IF(G6&gt;0,G6*8.4%,0)</f>
-        <v>5271.8400000000011</v>
+        <v>0</v>
       </c>
       <c r="I6" s="15">
         <v>0</v>
@@ -2349,10 +2335,10 @@
       </c>
       <c r="L6" s="32">
         <f>J6+K6+H6+G6</f>
-        <v>130791.84000000003</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+        <v>62760.000000000007</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="12">
         <v>3</v>
       </c>
@@ -2366,19 +2352,16 @@
         <v>0.15820000000000001</v>
       </c>
       <c r="E7" s="34">
-        <v>63279.929836000025</v>
-      </c>
-      <c r="F7" s="128">
-        <f>E7</f>
-        <v>63279.929836000025</v>
-      </c>
+        <v>63280</v>
+      </c>
+      <c r="F7" s="128"/>
       <c r="G7" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>63280</v>
       </c>
       <c r="H7" s="61">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>5315.52</v>
       </c>
       <c r="I7" s="15">
         <v>0</v>
@@ -2393,10 +2376,10 @@
       </c>
       <c r="L7" s="32">
         <f t="shared" ref="L7:L9" si="2">J7+K7+H7+G7</f>
-        <v>63280</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+        <v>131875.52000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="12">
         <v>4</v>
       </c>
@@ -2440,7 +2423,7 @@
         <v>79200</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="12">
         <v>5</v>
       </c>
@@ -2454,11 +2437,11 @@
         <v>0.15920000000000001</v>
       </c>
       <c r="E9" s="34">
-        <v>63641.744816000049</v>
+        <v>63680</v>
       </c>
       <c r="F9" s="128">
         <f>E9</f>
-        <v>63641.744816000049</v>
+        <v>63680</v>
       </c>
       <c r="G9" s="58">
         <f>E9-F9</f>
@@ -2484,7 +2467,7 @@
         <v>63680</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="12">
         <v>6</v>
       </c>
@@ -2498,11 +2481,11 @@
         <v>0.17649999999999999</v>
       </c>
       <c r="E10" s="34">
-        <v>70558.843970000045</v>
+        <v>70600</v>
       </c>
       <c r="F10" s="128">
         <f>E10</f>
-        <v>70558.843970000045</v>
+        <v>70600</v>
       </c>
       <c r="G10" s="58">
         <f>E10-F10</f>
@@ -2528,7 +2511,7 @@
         <v>70600</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
         <v>10</v>
       </c>
@@ -2540,19 +2523,19 @@
       </c>
       <c r="E11" s="35">
         <f t="shared" ref="E11" si="3">SUM(E5:E10)</f>
-        <v>712654.20716642635</v>
+        <v>872595.47838215809</v>
       </c>
       <c r="F11" s="35">
         <f>SUM(F5:F10)</f>
-        <v>276680.51862200012</v>
+        <v>344271.84</v>
       </c>
       <c r="G11" s="42">
         <f>SUM(G5:G10)</f>
-        <v>435973.68854442623</v>
+        <v>528323.63838215801</v>
       </c>
       <c r="H11" s="42">
         <f t="shared" ref="H11:K11" si="4">SUM(H5:H10)</f>
-        <v>36621.789837731805</v>
+        <v>44379.185624101272</v>
       </c>
       <c r="I11" s="11">
         <f t="shared" si="4"/>
@@ -2568,10 +2551,10 @@
       </c>
       <c r="L11" s="42">
         <f>SUM(L5:L10)</f>
-        <v>872595.47838215809</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+        <v>972702.82400625932</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="130"/>
       <c r="B12" s="130"/>
       <c r="C12" s="130"/>
@@ -2585,10 +2568,10 @@
       <c r="K12" s="130"/>
       <c r="L12" s="130"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="L13" s="6"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
     </row>
@@ -2608,21 +2591,21 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" customWidth="1"/>
-    <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
-    <col min="8" max="8" width="12.6640625" customWidth="1"/>
-    <col min="9" max="9" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.44140625" style="21"/>
+    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="106" t="s">
         <v>69</v>
       </c>
@@ -2637,7 +2620,7 @@
       <c r="H1" s="131"/>
       <c r="I1" s="110"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>0</v>
       </c>
@@ -2666,7 +2649,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="12"/>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -2687,7 +2670,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="12">
         <v>1</v>
       </c>
@@ -2719,7 +2702,7 @@
         <v>680400</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="12">
         <v>2</v>
       </c>
@@ -2751,7 +2734,7 @@
         <v>706050</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="12">
         <v>3</v>
       </c>
@@ -2783,7 +2766,7 @@
         <v>711900</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="12">
         <v>4</v>
       </c>
@@ -2815,7 +2798,7 @@
         <v>891000</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="12">
         <v>5</v>
       </c>
@@ -2847,7 +2830,7 @@
         <v>716400</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="12">
         <v>6</v>
       </c>
@@ -2879,7 +2862,7 @@
         <v>794250</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="113" t="s">
         <v>10</v>
       </c>
@@ -2910,7 +2893,7 @@
         <v>4500000</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="51.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" ht="51.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="130"/>
       <c r="B11" s="130"/>
       <c r="C11" s="130"/>
@@ -2921,10 +2904,10 @@
       <c r="H11" s="130"/>
       <c r="I11" s="130"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="I12" s="6"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
     </row>
@@ -2942,12 +2925,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="13.109375" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="137" t="s">
         <v>27</v>
       </c>
@@ -2958,7 +2941,7 @@
       <c r="F1" s="78"/>
       <c r="G1" s="78"/>
     </row>
-    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="140" t="s">
         <v>55</v>
       </c>
@@ -2971,7 +2954,7 @@
       <c r="F2" s="79"/>
       <c r="G2" s="79"/>
     </row>
-    <row r="3" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A3" s="145" t="s">
         <v>0</v>
       </c>
@@ -2994,7 +2977,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="146"/>
       <c r="B4" s="146"/>
       <c r="C4" s="146"/>
@@ -3003,7 +2986,7 @@
       <c r="F4" s="133"/>
       <c r="G4" s="133"/>
     </row>
-    <row r="5" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="80">
         <v>1</v>
       </c>
@@ -3026,7 +3009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="80">
         <v>2</v>
       </c>
@@ -3049,7 +3032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="80">
         <v>3</v>
       </c>
@@ -3072,7 +3055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="80">
         <v>4</v>
       </c>
@@ -3095,7 +3078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="80">
         <v>5</v>
       </c>
@@ -3118,7 +3101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="85">
         <v>6</v>
       </c>
@@ -3141,7 +3124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="90" t="s">
         <v>10</v>
       </c>
@@ -3160,7 +3143,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="134"/>
       <c r="B12" s="135"/>
       <c r="C12" s="135"/>
